--- a/PD Topics.xlsx
+++ b/PD Topics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\festi\Desktop\math-camp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4431251-15BE-4381-BC7B-D04511A1EDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8410C1DF-2B27-4A83-98C9-8D74B5937DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D55A69C6-995B-4BDD-8F4D-FCAAA8935CD0}"/>
   </bookViews>
@@ -542,7 +542,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1"/>
     </row>
